--- a/reports/pdf_change_20261030.xlsx
+++ b/reports/pdf_change_20261030.xlsx
@@ -560,7 +560,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,566억   ·   현금 4억(0.1%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 2종목  /  매도 5종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,493억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 2종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -656,7 +656,7 @@
         <v>65</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1372961754</v>
+        <v>1372962555</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -677,7 +677,7 @@
         <v>-102</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-906408228</v>
+        <v>-906408756</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -700,7 +700,7 @@
         <v>12</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1245282523</v>
+        <v>1245283250</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>-36</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-844501941</v>
+        <v>-844502434</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         <v>-32</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-927202696</v>
+        <v>-927203237</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
         <v>-4</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-884659519</v>
+        <v>-884660036</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>-3</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-133146228</v>
+        <v>-133146305</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
     <row r="12" ht="19" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,983억   ·   현금 74억(2.5%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 2,943억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B12" s="4" t="n"/>
@@ -845,7 +845,7 @@
     <row r="15" ht="19" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,229억   ·   현금 36억(1.7%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 6종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,154억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 6종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B15" s="4" t="n"/>
@@ -941,7 +941,7 @@
         <v>249</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>4658629547</v>
+        <v>4658630525</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
         <v>-695</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-4097915829</v>
+        <v>-4097916689</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>187</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2192736477</v>
+        <v>2192736938</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>-130</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-3017508905</v>
+        <v>-3017509538</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>61</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>4247724074</v>
+        <v>4247724965</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>-119</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-1192976548</v>
+        <v>-1192976798</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
         <v>61</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2982357994</v>
+        <v>2982358620</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>-101</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-917538815</v>
+        <v>-917539008</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>59</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3372553111</v>
+        <v>3372553819</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
         <v>-100</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1577455473</v>
+        <v>-1577455804</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2177755653</v>
+        <v>2177756110</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>-94</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-2476571743</v>
+        <v>-2476572262</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>-83</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-2657328797</v>
+        <v>-2657329355</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>-59</v>
       </c>
       <c r="I25" s="15" t="n">
-        <v>-1133366740</v>
+        <v>-1133366978</v>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>-51</v>
       </c>
       <c r="I26" s="15" t="n">
-        <v>-2245122673</v>
+        <v>-2245123144</v>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
@@ -1282,7 +1282,7 @@
     <row r="28" ht="19" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,074억   ·   현금 1억(0.1%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 0종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,054억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B28" s="4" t="n"/>
@@ -1378,7 +1378,7 @@
         <v>37</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>545742708</v>
+        <v>547096692</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 253억   ·   현금 1억(0.6%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 3종목  /  매도 2종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 245억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 3종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1495,11 +1495,11 @@
         <v>68</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>68282880</v>
+        <v>65018860</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>3.56%→3.82%</t>
+          <t>3.50%→3.76%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -1516,11 +1516,11 @@
         <v>-75</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-45216000</v>
+        <v>-42911987</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>1.34%→1.16%</t>
+          <t>1.32%→1.14%</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -1539,11 +1539,11 @@
         <v>61</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>24126720</v>
+        <v>24243832</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>0.29%→0.39%</t>
+          <t>0.30%→0.40%</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -1560,11 +1560,11 @@
         <v>-4</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-13363200</v>
+        <v>-12287996</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>1.00%→0.94%</t>
+          <t>0.95%→0.90%</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -1583,7 +1583,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>32960000</v>
+        <v>31679990</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 419억   ·   현금 3억(0.6%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 1종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 415억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B40" s="4" t="n"/>
@@ -1705,7 +1705,7 @@
         <v>-17</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-366863529</v>
+        <v>-366863657</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,037억   ·   현금 65억(6.3%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,025억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -1817,7 +1817,7 @@
         <v>6</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>76825767</v>
+        <v>76936426</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 913억   ·   현금 4억(0.4%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 2종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 907억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -1934,7 +1934,7 @@
         <v>723</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>1221724969</v>
+        <v>1228911733</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>-163</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1184602082</v>
+        <v>-1191570471</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>-6</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-319769887</v>
+        <v>-321650925</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 308억   ·   현금 2억(0.6%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 3종목  /  매도 5종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 301억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 3종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -2095,7 +2095,7 @@
         <v>27</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>150953724</v>
+        <v>150953832</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>-46</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-142340066</v>
+        <v>-142340168</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>24</v>
       </c>
       <c r="C60" s="11" t="n">
-        <v>193996754</v>
+        <v>193996892</v>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>-37</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-150629554</v>
+        <v>-150629662</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>16</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>127377730</v>
+        <v>127377821</v>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>-10</v>
       </c>
       <c r="I61" s="15" t="n">
-        <v>-95356477</v>
+        <v>-95356545</v>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>-9</v>
       </c>
       <c r="I62" s="15" t="n">
-        <v>-204227051</v>
+        <v>-204227197</v>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
         <v>-4</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-39742391</v>
+        <v>-39742419</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
     <row r="65" ht="19" customHeight="1">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,218억   ·   현금 20억(0.5%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ SOL 코리아메가테크액티브  (신한)      순자산 ≈ 4,113억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B65" s="4" t="n"/>
@@ -2300,7 +2300,7 @@
     <row r="68" ht="19" customHeight="1">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,287억   ·   현금 47억(1.4%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ WON 반도체밸류체인액티브  (우리)      순자산 ≈ 3,254억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B68" s="4" t="n"/>
@@ -2324,7 +2324,7 @@
     <row r="71" ht="19" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코리아테크액티브  (미래에셋)      순자산 ≈ 2,650억   ·   현금 31억(1.2%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 5종목  /  매도 2종목</t>
+          <t>■ TIGER 코리아테크액티브  (미래에셋)      순자산 ≈ 2,623억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 5종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B71" s="4" t="n"/>
@@ -2420,7 +2420,7 @@
         <v>20</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>1338634000</v>
+        <v>1338633829</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>-81</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-14676552000</v>
+        <v>-14676550121</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>16</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>2076835200</v>
+        <v>2076834934</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>-3</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-289126200</v>
+        <v>-289126163</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>15</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>1380027000</v>
+        <v>1380026823</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>11</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>8187223000</v>
+        <v>8187221952</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>7</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>1061691400</v>
+        <v>1061691264</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
     <row r="80" ht="19" customHeight="1">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 비메모리반도체액티브  (KB)      순자산 ≈ 2,226억   ·   현금 -3억(-0.1%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 1종목</t>
+          <t>■ RISE 비메모리반도체액티브  (KB)      순자산 ≈ 2,164억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B80" s="4" t="n"/>
@@ -2681,7 +2681,7 @@
         <v>12</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>1219392000</v>
+        <v>1213823722</v>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         <v>-14</v>
       </c>
       <c r="I83" s="15" t="n">
-        <v>-1085364000</v>
+        <v>-1080407752</v>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
     <row r="85" ht="19" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 827억   ·   현금 6억(0.7%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ DAISHIN AI반도체&amp;인프라액티브  (대신)      순자산 ≈ 808억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B85" s="4" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="88" ht="19" customHeight="1">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 374억   ·   현금 3억(0.8%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 7종목  /  매도 6종목</t>
+          <t>■ KoAct AI인프라액티브  (삼성액티브)      순자산 ≈ 366억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 7종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B88" s="4" t="n"/>
@@ -3123,7 +3123,7 @@
     <row r="99" ht="19" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 534억   ·   현금 -2억(-0.4%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ PLUS AI반도체소부장액티브  (한화)      순자산 ≈ 540억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B99" s="4" t="n"/>
@@ -3147,7 +3147,7 @@
     <row r="102" ht="19" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 반도체소부장액티브  (KB)      순자산 ≈ 174억   ·   현금 2억(1.0%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 14종목</t>
+          <t>■ RISE 반도체소부장액티브  (KB)      순자산 ≈ 170억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 1종목  /  매도 14종목</t>
         </is>
       </c>
       <c r="B102" s="4" t="n"/>
@@ -3243,7 +3243,7 @@
         <v>399</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>243390122</v>
+        <v>243390000</v>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>-24</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>-8505604</v>
+        <v>-8505600</v>
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
@@ -3292,7 +3292,7 @@
         <v>-10</v>
       </c>
       <c r="I106" s="15" t="n">
-        <v>-18260009</v>
+        <v>-18260000</v>
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>-7</v>
       </c>
       <c r="I107" s="15" t="n">
-        <v>-11116006</v>
+        <v>-11116000</v>
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
@@ -3341,23 +3341,23 @@
       <c r="E108" s="17" t="n"/>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-24680012</v>
+        <v>-23560000</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>8.30%→8.10%</t>
+          <t>8.18%→8.19%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>281→276</t>
+          <t>297→292</t>
         </is>
       </c>
     </row>
@@ -3369,23 +3369,23 @@
       <c r="E109" s="17" t="n"/>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-20880010</v>
+        <v>-24060000</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.50%</t>
+          <t>7.44%→7.30%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>307→302</t>
+          <t>260→255</t>
         </is>
       </c>
     </row>
@@ -3397,23 +3397,23 @@
       <c r="E110" s="17" t="n"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-24060012</v>
+        <v>-12340000</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>7.44%→7.30%</t>
+          <t>4.80%→4.71%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>260→255</t>
+          <t>326→321</t>
         </is>
       </c>
     </row>
@@ -3425,23 +3425,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-23560012</v>
+        <v>-8260000</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>8.18%→8.19%</t>
+          <t>3.12%→3.13%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>297→292</t>
+          <t>324→319</t>
         </is>
       </c>
     </row>
@@ -3453,23 +3453,23 @@
       <c r="E112" s="17" t="n"/>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H112" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I112" s="15" t="n">
-        <v>-12340006</v>
+        <v>-24680000</v>
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>4.80%→4.71%</t>
+          <t>8.30%→8.10%</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
         <is>
-          <t>326→321</t>
+          <t>281→276</t>
         </is>
       </c>
     </row>
@@ -3481,23 +3481,23 @@
       <c r="E113" s="17" t="n"/>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-8260004</v>
+        <v>-20880000</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>3.12%→3.13%</t>
+          <t>7.69%→7.50%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>324→319</t>
+          <t>307→302</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
         <v>-4</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-8272004</v>
+        <v>-8272000</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>-4</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>-14816007</v>
+        <v>-14816000</v>
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
@@ -3565,23 +3565,23 @@
       <c r="E116" s="17" t="n"/>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-11616006</v>
+        <v>-13536000</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.55%</t>
+          <t>4.44%→4.38%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>157→154</t>
+          <t>166→163</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
         <v>-3</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-23304012</v>
+        <v>-23304000</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
@@ -3621,30 +3621,30 @@
       <c r="E118" s="17" t="n"/>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-13536007</v>
+        <v>-11616000</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>4.44%→4.38%</t>
+          <t>3.84%→3.55%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>166→163</t>
+          <t>157→154</t>
         </is>
       </c>
     </row>
     <row r="120" ht="19" customHeight="1">
       <c r="A120" s="3" t="inlineStr">
         <is>
-          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 149억   ·   현금 -8억(-5.2%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 4종목  /  매도 3종목</t>
+          <t>■ DS AI반도체액티브  (DS)      순자산 ≈ 152억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B120" s="4" t="n"/>
@@ -3740,7 +3740,7 @@
         <v>397</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>138116379</v>
+        <v>142062480</v>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>-131</v>
       </c>
       <c r="I123" s="15" t="n">
-        <v>-196008862</v>
+        <v>-201609000</v>
       </c>
       <c r="J123" s="16" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>150</v>
       </c>
       <c r="C124" s="11" t="n">
-        <v>228375130</v>
+        <v>234900000</v>
       </c>
       <c r="D124" s="12" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>-26</v>
       </c>
       <c r="I124" s="15" t="n">
-        <v>-197925113</v>
+        <v>-203580000</v>
       </c>
       <c r="J124" s="16" t="inlineStr">
         <is>
@@ -3828,7 +3828,7 @@
         <v>19</v>
       </c>
       <c r="C125" s="11" t="n">
-        <v>154280088</v>
+        <v>158688000</v>
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>-10</v>
       </c>
       <c r="I125" s="15" t="n">
-        <v>-109725063</v>
+        <v>-112860000</v>
       </c>
       <c r="J125" s="16" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>3</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>56175032</v>
+        <v>57780000</v>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
     <row r="128" ht="19" customHeight="1">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 2차전지액티브  (KB)      순자산 ≈ 2,095억   ·   현금 11억(0.5%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 3종목  /  매도 1종목</t>
+          <t>■ RISE 2차전지액티브  (KB)      순자산 ≈ 2,024억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B128" s="4" t="n"/>
@@ -3989,7 +3989,7 @@
         <v>27</v>
       </c>
       <c r="C131" s="11" t="n">
-        <v>1935231994</v>
+        <v>1937559976</v>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
@@ -4010,7 +4010,7 @@
         <v>-18</v>
       </c>
       <c r="I131" s="15" t="n">
-        <v>-4816377849</v>
+        <v>-4822171697</v>
       </c>
       <c r="J131" s="16" t="inlineStr">
         <is>
@@ -4033,7 +4033,7 @@
         <v>12</v>
       </c>
       <c r="C132" s="11" t="n">
-        <v>950902857</v>
+        <v>952046743</v>
       </c>
       <c r="D132" s="12" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>3</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>1085106880</v>
+        <v>1086412206</v>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
     <row r="135" ht="19" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 287억   ·   현금 2억(0.5%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 2종목  /  매도 2종목</t>
+          <t>■ KoAct 수소전력ESS인프라액티브  (삼성액티브)      순자산 ≈ 281억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 2종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B135" s="4" t="n"/>
@@ -4178,7 +4178,7 @@
         <v>42</v>
       </c>
       <c r="C138" s="11" t="n">
-        <v>54285000</v>
+        <v>55271980</v>
       </c>
       <c r="D138" s="12" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>-95</v>
       </c>
       <c r="I138" s="15" t="n">
-        <v>-134543750</v>
+        <v>-136989951</v>
       </c>
       <c r="J138" s="16" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>32</v>
       </c>
       <c r="C139" s="11" t="n">
-        <v>83864000</v>
+        <v>85388770</v>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>-3</v>
       </c>
       <c r="I139" s="15" t="n">
-        <v>-72682500</v>
+        <v>-74003974</v>
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
     <row r="141" ht="19" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 161억   ·   현금 2억(1.0%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ ACE 2차전지&amp;친환경차액티브  (한국투자)      순자산 ≈ 157억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B141" s="4" t="n"/>
@@ -4283,7 +4283,7 @@
     <row r="144" ht="19" customHeight="1">
       <c r="A144" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 89억   ·   현금 3억(3.4%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 반도체&amp;2차전지핵심소재액티브  (삼성액티브)      순자산 ≈ 87억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B144" s="4" t="n"/>
@@ -4307,7 +4307,7 @@
     <row r="147" ht="19" customHeight="1">
       <c r="A147" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 59억   ·   현금 1억(1.6%)      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 58억      당일 2026-10-30  vs  전영업일 2026-10-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B147" s="4" t="n"/>

--- a/reports/pdf_change_20261030.xlsx
+++ b/reports/pdf_change_20261030.xlsx
@@ -3341,23 +3341,23 @@
       <c r="E108" s="17" t="n"/>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-23560000</v>
+        <v>-24680000</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>8.18%→8.19%</t>
+          <t>8.30%→8.10%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>297→292</t>
+          <t>281→276</t>
         </is>
       </c>
     </row>
@@ -3369,23 +3369,23 @@
       <c r="E109" s="17" t="n"/>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-24060000</v>
+        <v>-20880000</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>7.44%→7.30%</t>
+          <t>7.69%→7.50%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>260→255</t>
+          <t>307→302</t>
         </is>
       </c>
     </row>
@@ -3397,23 +3397,23 @@
       <c r="E110" s="17" t="n"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-12340000</v>
+        <v>-24060000</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>4.80%→4.71%</t>
+          <t>7.44%→7.30%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>326→321</t>
+          <t>260→255</t>
         </is>
       </c>
     </row>
@@ -3425,23 +3425,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-8260000</v>
+        <v>-23560000</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>3.12%→3.13%</t>
+          <t>8.18%→8.19%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>324→319</t>
+          <t>297→292</t>
         </is>
       </c>
     </row>
@@ -3453,23 +3453,23 @@
       <c r="E112" s="17" t="n"/>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H112" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I112" s="15" t="n">
-        <v>-24680000</v>
+        <v>-12340000</v>
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>8.30%→8.10%</t>
+          <t>4.80%→4.71%</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
         <is>
-          <t>281→276</t>
+          <t>326→321</t>
         </is>
       </c>
     </row>
@@ -3481,23 +3481,23 @@
       <c r="E113" s="17" t="n"/>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-20880000</v>
+        <v>-8260000</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.50%</t>
+          <t>3.12%→3.13%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>307→302</t>
+          <t>324→319</t>
         </is>
       </c>
     </row>
@@ -3565,23 +3565,23 @@
       <c r="E116" s="17" t="n"/>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-13536000</v>
+        <v>-11616000</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>4.44%→4.38%</t>
+          <t>3.84%→3.55%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>166→163</t>
+          <t>157→154</t>
         </is>
       </c>
     </row>
@@ -3593,23 +3593,23 @@
       <c r="E117" s="17" t="n"/>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-23304000</v>
+        <v>-13536000</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.81%</t>
+          <t>4.44%→4.38%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>172→169</t>
+          <t>166→163</t>
         </is>
       </c>
     </row>
@@ -3621,23 +3621,23 @@
       <c r="E118" s="17" t="n"/>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-11616000</v>
+        <v>-23304000</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.55%</t>
+          <t>7.69%→7.81%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>157→154</t>
+          <t>172→169</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261030.xlsx
+++ b/reports/pdf_change_20261030.xlsx
@@ -3341,23 +3341,23 @@
       <c r="E108" s="17" t="n"/>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-24680000</v>
+        <v>-20880000</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>8.30%→8.10%</t>
+          <t>7.69%→7.50%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>281→276</t>
+          <t>307→302</t>
         </is>
       </c>
     </row>
@@ -3369,23 +3369,23 @@
       <c r="E109" s="17" t="n"/>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-20880000</v>
+        <v>-23560000</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.50%</t>
+          <t>8.18%→8.19%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>307→302</t>
+          <t>297→292</t>
         </is>
       </c>
     </row>
@@ -3425,23 +3425,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-23560000</v>
+        <v>-24680000</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>8.18%→8.19%</t>
+          <t>8.30%→8.10%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>297→292</t>
+          <t>281→276</t>
         </is>
       </c>
     </row>
@@ -3565,23 +3565,23 @@
       <c r="E116" s="17" t="n"/>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-11616000</v>
+        <v>-23304000</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.55%</t>
+          <t>7.69%→7.81%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>157→154</t>
+          <t>172→169</t>
         </is>
       </c>
     </row>
@@ -3621,23 +3621,23 @@
       <c r="E118" s="17" t="n"/>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-23304000</v>
+        <v>-11616000</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.81%</t>
+          <t>3.84%→3.55%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>172→169</t>
+          <t>157→154</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261030.xlsx
+++ b/reports/pdf_change_20261030.xlsx
@@ -1022,23 +1022,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>4247724965</v>
+        <v>2982358620</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.96%→2.96%</t>
+          <t>2.32%→3.69%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>29→90</t>
+          <t>99→160</t>
         </is>
       </c>
       <c r="G20" s="14" t="inlineStr">
@@ -1066,23 +1066,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>61</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2982358620</v>
+        <v>4247724965</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.32%→3.69%</t>
+          <t>0.96%→2.96%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>99→160</t>
+          <t>29→90</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -3341,23 +3341,23 @@
       <c r="E108" s="17" t="n"/>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-20880000</v>
+        <v>-23560000</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.50%</t>
+          <t>8.18%→8.19%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>307→302</t>
+          <t>297→292</t>
         </is>
       </c>
     </row>
@@ -3369,23 +3369,23 @@
       <c r="E109" s="17" t="n"/>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-23560000</v>
+        <v>-12340000</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>8.18%→8.19%</t>
+          <t>4.80%→4.71%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>297→292</t>
+          <t>326→321</t>
         </is>
       </c>
     </row>
@@ -3397,23 +3397,23 @@
       <c r="E110" s="17" t="n"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-24060000</v>
+        <v>-20880000</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>7.44%→7.30%</t>
+          <t>7.69%→7.50%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>260→255</t>
+          <t>307→302</t>
         </is>
       </c>
     </row>
@@ -3425,23 +3425,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-24680000</v>
+        <v>-24060000</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>8.30%→8.10%</t>
+          <t>7.44%→7.30%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>281→276</t>
+          <t>260→255</t>
         </is>
       </c>
     </row>
@@ -3453,23 +3453,23 @@
       <c r="E112" s="17" t="n"/>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="H112" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I112" s="15" t="n">
-        <v>-12340000</v>
+        <v>-8260000</v>
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>4.80%→4.71%</t>
+          <t>3.12%→3.13%</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
         <is>
-          <t>326→321</t>
+          <t>324→319</t>
         </is>
       </c>
     </row>
@@ -3481,23 +3481,23 @@
       <c r="E113" s="17" t="n"/>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-8260000</v>
+        <v>-24680000</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>3.12%→3.13%</t>
+          <t>8.30%→8.10%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>324→319</t>
+          <t>281→276</t>
         </is>
       </c>
     </row>
@@ -3509,23 +3509,23 @@
       <c r="E114" s="17" t="n"/>
       <c r="G114" s="14" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I114" s="15" t="n">
-        <v>-8272000</v>
+        <v>-14816000</v>
       </c>
       <c r="J114" s="16" t="inlineStr">
         <is>
-          <t>3.04%→3.01%</t>
+          <t>5.99%→5.80%</t>
         </is>
       </c>
       <c r="K114" s="13" t="inlineStr">
         <is>
-          <t>249→245</t>
+          <t>267→263</t>
         </is>
       </c>
     </row>
@@ -3537,23 +3537,23 @@
       <c r="E115" s="17" t="n"/>
       <c r="G115" s="14" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="H115" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I115" s="15" t="n">
-        <v>-14816000</v>
+        <v>-8272000</v>
       </c>
       <c r="J115" s="16" t="inlineStr">
         <is>
-          <t>5.99%→5.80%</t>
+          <t>3.04%→3.01%</t>
         </is>
       </c>
       <c r="K115" s="13" t="inlineStr">
         <is>
-          <t>267→263</t>
+          <t>249→245</t>
         </is>
       </c>
     </row>
@@ -3565,23 +3565,23 @@
       <c r="E116" s="17" t="n"/>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-23304000</v>
+        <v>-13536000</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.81%</t>
+          <t>4.44%→4.38%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>172→169</t>
+          <t>166→163</t>
         </is>
       </c>
     </row>
@@ -3593,23 +3593,23 @@
       <c r="E117" s="17" t="n"/>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-13536000</v>
+        <v>-23304000</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>4.44%→4.38%</t>
+          <t>7.69%→7.81%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>166→163</t>
+          <t>172→169</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_change_20261030.xlsx
+++ b/reports/pdf_change_20261030.xlsx
@@ -3341,23 +3341,23 @@
       <c r="E108" s="17" t="n"/>
       <c r="G108" s="14" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I108" s="15" t="n">
-        <v>-23560000</v>
+        <v>-20880000</v>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>8.18%→8.19%</t>
+          <t>7.69%→7.50%</t>
         </is>
       </c>
       <c r="K108" s="13" t="inlineStr">
         <is>
-          <t>297→292</t>
+          <t>307→302</t>
         </is>
       </c>
     </row>
@@ -3369,23 +3369,23 @@
       <c r="E109" s="17" t="n"/>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I109" s="15" t="n">
-        <v>-12340000</v>
+        <v>-23560000</v>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>4.80%→4.71%</t>
+          <t>8.18%→8.19%</t>
         </is>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
-          <t>326→321</t>
+          <t>297→292</t>
         </is>
       </c>
     </row>
@@ -3397,23 +3397,23 @@
       <c r="E110" s="17" t="n"/>
       <c r="G110" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I110" s="15" t="n">
-        <v>-20880000</v>
+        <v>-8260000</v>
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.50%</t>
+          <t>3.12%→3.13%</t>
         </is>
       </c>
       <c r="K110" s="13" t="inlineStr">
         <is>
-          <t>307→302</t>
+          <t>324→319</t>
         </is>
       </c>
     </row>
@@ -3425,23 +3425,23 @@
       <c r="E111" s="17" t="n"/>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>피에스케이</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I111" s="15" t="n">
-        <v>-24060000</v>
+        <v>-24680000</v>
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>7.44%→7.30%</t>
+          <t>8.30%→8.10%</t>
         </is>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
-          <t>260→255</t>
+          <t>281→276</t>
         </is>
       </c>
     </row>
@@ -3453,23 +3453,23 @@
       <c r="E112" s="17" t="n"/>
       <c r="G112" s="14" t="inlineStr">
         <is>
-          <t>동진쎄미켐</t>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="H112" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I112" s="15" t="n">
-        <v>-8260000</v>
+        <v>-12340000</v>
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>3.12%→3.13%</t>
+          <t>4.80%→4.71%</t>
         </is>
       </c>
       <c r="K112" s="13" t="inlineStr">
         <is>
-          <t>324→319</t>
+          <t>326→321</t>
         </is>
       </c>
     </row>
@@ -3481,23 +3481,23 @@
       <c r="E113" s="17" t="n"/>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>피에스케이</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
         <v>-5</v>
       </c>
       <c r="I113" s="15" t="n">
-        <v>-24680000</v>
+        <v>-24060000</v>
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>8.30%→8.10%</t>
+          <t>7.44%→7.30%</t>
         </is>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
-          <t>281→276</t>
+          <t>260→255</t>
         </is>
       </c>
     </row>
@@ -3565,23 +3565,23 @@
       <c r="E116" s="17" t="n"/>
       <c r="G116" s="14" t="inlineStr">
         <is>
-          <t>유진테크</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H116" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I116" s="15" t="n">
-        <v>-13536000</v>
+        <v>-23304000</v>
       </c>
       <c r="J116" s="16" t="inlineStr">
         <is>
-          <t>4.44%→4.38%</t>
+          <t>7.69%→7.81%</t>
         </is>
       </c>
       <c r="K116" s="13" t="inlineStr">
         <is>
-          <t>166→163</t>
+          <t>172→169</t>
         </is>
       </c>
     </row>
@@ -3593,23 +3593,23 @@
       <c r="E117" s="17" t="n"/>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H117" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I117" s="15" t="n">
-        <v>-23304000</v>
+        <v>-11616000</v>
       </c>
       <c r="J117" s="16" t="inlineStr">
         <is>
-          <t>7.69%→7.81%</t>
+          <t>3.84%→3.55%</t>
         </is>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
-          <t>172→169</t>
+          <t>157→154</t>
         </is>
       </c>
     </row>
@@ -3621,23 +3621,23 @@
       <c r="E118" s="17" t="n"/>
       <c r="G118" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>유진테크</t>
         </is>
       </c>
       <c r="H118" s="15" t="n">
         <v>-3</v>
       </c>
       <c r="I118" s="15" t="n">
-        <v>-11616000</v>
+        <v>-13536000</v>
       </c>
       <c r="J118" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.55%</t>
+          <t>4.44%→4.38%</t>
         </is>
       </c>
       <c r="K118" s="13" t="inlineStr">
         <is>
-          <t>157→154</t>
+          <t>166→163</t>
         </is>
       </c>
     </row>
